--- a/reach-tracker.xlsx
+++ b/reach-tracker.xlsx
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
